--- a/labeled/Add_Eating/July/tcn_predictions_both_regression.xlsx
+++ b/labeled/Add_Eating/July/tcn_predictions_both_regression.xlsx
@@ -442,810 +442,810 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74.28571319580078</v>
+        <v>60</v>
       </c>
       <c r="B2" t="n">
-        <v>70.75817108154297</v>
+        <v>61.0377197265625</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54.66666793823242</v>
+        <v>20.60000038146973</v>
       </c>
       <c r="B3" t="n">
-        <v>52.10166168212891</v>
+        <v>15.24424839019775</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>32.24206161499023</v>
+        <v>12.73261547088623</v>
       </c>
       <c r="B4" t="n">
-        <v>43.50763702392578</v>
+        <v>11.17495536804199</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>31</v>
+        <v>37.59999847412109</v>
       </c>
       <c r="B5" t="n">
-        <v>36.1308708190918</v>
+        <v>30.63302993774414</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>39.29999923706055</v>
+        <v>34.37805938720703</v>
       </c>
       <c r="B6" t="n">
-        <v>24.75396728515625</v>
+        <v>35.17618179321289</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>29.39999961853027</v>
+        <v>22.60000038146973</v>
       </c>
       <c r="B7" t="n">
-        <v>27.30856513977051</v>
+        <v>27.07966613769531</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>34.37805938720703</v>
+        <v>48</v>
       </c>
       <c r="B8" t="n">
-        <v>26.68507194519043</v>
+        <v>44.0576171875</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>32.22331237792969</v>
+        <v>28.7952995300293</v>
       </c>
       <c r="B9" t="n">
-        <v>37.35955429077148</v>
+        <v>27.69060707092285</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>59.40000152587891</v>
+        <v>9.990205764770508</v>
       </c>
       <c r="B10" t="n">
-        <v>57.43468856811523</v>
+        <v>10.4569149017334</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131.6999969482422</v>
+        <v>20.33730125427246</v>
       </c>
       <c r="B11" t="n">
-        <v>129.3425750732422</v>
+        <v>24.45772933959961</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>85.69999694824219</v>
+        <v>11.14285755157471</v>
       </c>
       <c r="B12" t="n">
-        <v>87.29299926757812</v>
+        <v>9.950004577636719</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>45.80952453613281</v>
+        <v>33.90000152587891</v>
       </c>
       <c r="B13" t="n">
-        <v>44.26318740844727</v>
+        <v>23.74174690246582</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103.8000030517578</v>
+        <v>40</v>
       </c>
       <c r="B14" t="n">
-        <v>69.59959411621094</v>
+        <v>49.49699783325195</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>40</v>
+        <v>9.162561416625977</v>
       </c>
       <c r="B15" t="n">
-        <v>37.29005813598633</v>
+        <v>8.599762916564941</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>32.24206161499023</v>
+        <v>36.63075256347656</v>
       </c>
       <c r="B16" t="n">
-        <v>32.09922027587891</v>
+        <v>24.98045921325684</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>39.29999923706055</v>
+        <v>39.68254089355469</v>
       </c>
       <c r="B17" t="n">
-        <v>27.69659996032715</v>
+        <v>40.43139266967773</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>34.37805938720703</v>
+        <v>20.66601371765137</v>
       </c>
       <c r="B18" t="n">
-        <v>23.51472854614258</v>
+        <v>24.5894832611084</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>54.90000152587891</v>
+        <v>27.6785717010498</v>
       </c>
       <c r="B19" t="n">
-        <v>56.9919548034668</v>
+        <v>26.83601760864258</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>68.85713958740234</v>
+        <v>15.10000038146973</v>
       </c>
       <c r="B20" t="n">
-        <v>51.5525016784668</v>
+        <v>16.26782417297363</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>14.6245059967041</v>
+        <v>80</v>
       </c>
       <c r="B21" t="n">
-        <v>21.20942687988281</v>
+        <v>74.27167510986328</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>57.09999847412109</v>
+        <v>13.4285717010498</v>
       </c>
       <c r="B22" t="n">
-        <v>51.64702987670898</v>
+        <v>17.29689407348633</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>59.40000152587891</v>
+        <v>11.11111068725586</v>
       </c>
       <c r="B23" t="n">
-        <v>52.99256896972656</v>
+        <v>11.31690406799316</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>27.90476226806641</v>
+        <v>6.660137176513672</v>
       </c>
       <c r="B24" t="n">
-        <v>18.49523544311523</v>
+        <v>16.43674659729004</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>29.39999961853027</v>
+        <v>27.90476226806641</v>
       </c>
       <c r="B25" t="n">
-        <v>29.97563362121582</v>
+        <v>33.58940124511719</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>32.24206161499023</v>
+        <v>16.5714282989502</v>
       </c>
       <c r="B26" t="n">
-        <v>40.50503540039062</v>
+        <v>17.44294738769531</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>68.85713958740234</v>
+        <v>17.80952453613281</v>
       </c>
       <c r="B27" t="n">
-        <v>58.498046875</v>
+        <v>11.96884632110596</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>58</v>
+        <v>15.083251953125</v>
       </c>
       <c r="B28" t="n">
-        <v>41.99340438842773</v>
+        <v>14.37854671478271</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>60</v>
+        <v>32.41919708251953</v>
       </c>
       <c r="B29" t="n">
-        <v>52.15044021606445</v>
+        <v>38.05093002319336</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131.6999969482422</v>
+        <v>15.08875751495361</v>
       </c>
       <c r="B30" t="n">
-        <v>102.2392272949219</v>
+        <v>15.70514869689941</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>32.24206161499023</v>
+        <v>39.68254089355469</v>
       </c>
       <c r="B31" t="n">
-        <v>38.17392349243164</v>
+        <v>46.64896011352539</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>85.69999694824219</v>
+        <v>25.46523094177246</v>
       </c>
       <c r="B32" t="n">
-        <v>71.40010833740234</v>
+        <v>24.01793670654297</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>63.0476188659668</v>
+        <v>91.5</v>
       </c>
       <c r="B33" t="n">
-        <v>57.28910827636719</v>
+        <v>95.29362487792969</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>17.80952453613281</v>
+        <v>80</v>
       </c>
       <c r="B34" t="n">
-        <v>24.16741943359375</v>
+        <v>72.04434204101562</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>40.47618865966797</v>
+        <v>35.16160583496094</v>
       </c>
       <c r="B35" t="n">
-        <v>34.69205856323242</v>
+        <v>28.14466285705566</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>45.80952453613281</v>
+        <v>10.4761905670166</v>
       </c>
       <c r="B36" t="n">
-        <v>43.17900466918945</v>
+        <v>13.55770301818848</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>62.09523773193359</v>
+        <v>35.20000076293945</v>
       </c>
       <c r="B37" t="n">
-        <v>46.98872756958008</v>
+        <v>33.27633666992188</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>69.90476226806641</v>
+        <v>51.90989303588867</v>
       </c>
       <c r="B38" t="n">
-        <v>59.0482063293457</v>
+        <v>47.93557739257812</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>40</v>
+        <v>43.79999923706055</v>
       </c>
       <c r="B39" t="n">
-        <v>31.97934532165527</v>
+        <v>45.83195877075195</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>45.80952453613281</v>
+        <v>23.5238094329834</v>
       </c>
       <c r="B40" t="n">
-        <v>39.38982772827148</v>
+        <v>24.1537914276123</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>28.40352630615234</v>
+        <v>39.68254089355469</v>
       </c>
       <c r="B41" t="n">
-        <v>27.33524131774902</v>
+        <v>44.95416259765625</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>36.23898315429688</v>
+        <v>11.65524005889893</v>
       </c>
       <c r="B42" t="n">
-        <v>24.50825691223145</v>
+        <v>14.82961654663086</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>28.20763969421387</v>
+        <v>14.66666698455811</v>
       </c>
       <c r="B43" t="n">
-        <v>28.37389755249023</v>
+        <v>18.7154541015625</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>60.82272338867188</v>
+        <v>60</v>
       </c>
       <c r="B44" t="n">
-        <v>62.44097900390625</v>
+        <v>57.28807830810547</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>68.85713958740234</v>
+        <v>23.01665115356445</v>
       </c>
       <c r="B45" t="n">
-        <v>59.68147277832031</v>
+        <v>26.64728736877441</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>40</v>
+        <v>19.0476188659668</v>
       </c>
       <c r="B46" t="n">
-        <v>41.63116455078125</v>
+        <v>26.51895332336426</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1.762977480888367</v>
+        <v>20</v>
       </c>
       <c r="B47" t="n">
-        <v>16.8674488067627</v>
+        <v>34.94650650024414</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>20.38095283508301</v>
+        <v>61.40000152587891</v>
       </c>
       <c r="B48" t="n">
-        <v>35.89688491821289</v>
+        <v>64.18421173095703</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>40</v>
+        <v>41.52381134033203</v>
       </c>
       <c r="B49" t="n">
-        <v>39.4705810546875</v>
+        <v>37.40254974365234</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131.6999969482422</v>
+        <v>32.24206161499023</v>
       </c>
       <c r="B50" t="n">
-        <v>135.6363372802734</v>
+        <v>33.51081848144531</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>36.29999923706055</v>
+        <v>23</v>
       </c>
       <c r="B51" t="n">
-        <v>35.21321487426758</v>
+        <v>26.57788848876953</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>58</v>
+        <v>90.19999694824219</v>
       </c>
       <c r="B52" t="n">
-        <v>56.65913009643555</v>
+        <v>83.15576171875</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>62.09523773193359</v>
+        <v>23.60000038146973</v>
       </c>
       <c r="B53" t="n">
-        <v>50.32457733154297</v>
+        <v>23.96372032165527</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>43.79999923706055</v>
+        <v>21.05778694152832</v>
       </c>
       <c r="B54" t="n">
-        <v>57.51017379760742</v>
+        <v>19.93966293334961</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>63.0476188659668</v>
+        <v>6.547618865966797</v>
       </c>
       <c r="B55" t="n">
-        <v>60.68623352050781</v>
+        <v>8.342134475708008</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>58</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="B56" t="n">
-        <v>46.51909637451172</v>
+        <v>20.8316822052002</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>87.80000305175781</v>
+        <v>21.89999961853027</v>
       </c>
       <c r="B57" t="n">
-        <v>84.95883178710938</v>
+        <v>21.28005409240723</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>92.90000152587891</v>
+        <v>9.06403923034668</v>
       </c>
       <c r="B58" t="n">
-        <v>70.55244445800781</v>
+        <v>18.51709747314453</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>10.47430801391602</v>
+        <v>71.80000305175781</v>
       </c>
       <c r="B59" t="n">
-        <v>26.36738395690918</v>
+        <v>75.739990234375</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>68.85713958740234</v>
+        <v>18</v>
       </c>
       <c r="B60" t="n">
-        <v>61.77890777587891</v>
+        <v>21.06497001647949</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131.6999969482422</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="B61" t="n">
-        <v>132.2522735595703</v>
+        <v>23.30783843994141</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>57.09999847412109</v>
+        <v>22.13516235351562</v>
       </c>
       <c r="B62" t="n">
-        <v>43.87292861938477</v>
+        <v>20.47330093383789</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>69.63761138916016</v>
+        <v>16.96428489685059</v>
       </c>
       <c r="B63" t="n">
-        <v>69.12708282470703</v>
+        <v>12.5278148651123</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>61.90476226806641</v>
+        <v>20</v>
       </c>
       <c r="B64" t="n">
-        <v>63.72720718383789</v>
+        <v>20.0888671875</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>91.5</v>
+        <v>39.68254089355469</v>
       </c>
       <c r="B65" t="n">
-        <v>77.83525848388672</v>
+        <v>44.47504425048828</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>31</v>
+        <v>23.11459350585938</v>
       </c>
       <c r="B66" t="n">
-        <v>34.58479309082031</v>
+        <v>23.68696022033691</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>40.47618865966797</v>
+        <v>20</v>
       </c>
       <c r="B67" t="n">
-        <v>38.09421920776367</v>
+        <v>31.2418384552002</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>85.69999694824219</v>
+        <v>44.79999923706055</v>
       </c>
       <c r="B68" t="n">
-        <v>86.16663360595703</v>
+        <v>45.25007629394531</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>44.57143020629883</v>
+        <v>14.6245059967041</v>
       </c>
       <c r="B69" t="n">
-        <v>47.39846420288086</v>
+        <v>15.35816383361816</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>53.20000076293945</v>
+        <v>80</v>
       </c>
       <c r="B70" t="n">
-        <v>42.91430282592773</v>
+        <v>71.99905395507812</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>87.80000305175781</v>
+        <v>20</v>
       </c>
       <c r="B71" t="n">
-        <v>91.49115753173828</v>
+        <v>31.21963691711426</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>69.63761138916016</v>
+        <v>35.90000152587891</v>
       </c>
       <c r="B72" t="n">
-        <v>56.90007400512695</v>
+        <v>38.19002532958984</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>59</v>
+        <v>29.60000038146973</v>
       </c>
       <c r="B73" t="n">
-        <v>47.86952972412109</v>
+        <v>25.05302619934082</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>53.20000076293945</v>
+        <v>19.84127044677734</v>
       </c>
       <c r="B74" t="n">
-        <v>48.14201354980469</v>
+        <v>27.3168888092041</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>58</v>
+        <v>8.275861740112305</v>
       </c>
       <c r="B75" t="n">
-        <v>63.41447067260742</v>
+        <v>20.05484008789062</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>68.85713958740234</v>
+        <v>6.206896781921387</v>
       </c>
       <c r="B76" t="n">
-        <v>61.69006729125977</v>
+        <v>11.4210901260376</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>59.40000152587891</v>
+        <v>13.88888931274414</v>
       </c>
       <c r="B77" t="n">
-        <v>51.90908432006836</v>
+        <v>17.77402114868164</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>12.74703598022461</v>
+        <v>60</v>
       </c>
       <c r="B78" t="n">
-        <v>37.46046829223633</v>
+        <v>63.71698379516602</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>103.8000030517578</v>
+        <v>58.70000076293945</v>
       </c>
       <c r="B79" t="n">
-        <v>79.46552276611328</v>
+        <v>54.8780403137207</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>59</v>
+        <v>39.5</v>
       </c>
       <c r="B80" t="n">
-        <v>51.69442749023438</v>
+        <v>44.15721893310547</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>61.90476226806641</v>
+        <v>17.36111068725586</v>
       </c>
       <c r="B81" t="n">
-        <v>62.26865386962891</v>
+        <v>20.97534942626953</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>28.20763969421387</v>
+        <v>57</v>
       </c>
       <c r="B82" t="n">
-        <v>20.92628288269043</v>
+        <v>52.78530120849609</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>85.69999694824219</v>
+        <v>73.40000152587891</v>
       </c>
       <c r="B83" t="n">
-        <v>84.74855041503906</v>
+        <v>81.25955200195312</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>103.8000030517578</v>
+        <v>21</v>
       </c>
       <c r="B84" t="n">
-        <v>101.562385559082</v>
+        <v>16.44359016418457</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>91.5</v>
+        <v>23.5</v>
       </c>
       <c r="B85" t="n">
-        <v>96.53246307373047</v>
+        <v>25.71222496032715</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>37.59999847412109</v>
+        <v>25.6611156463623</v>
       </c>
       <c r="B86" t="n">
-        <v>23.94695472717285</v>
+        <v>24.41497993469238</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>92.90000152587891</v>
+        <v>60</v>
       </c>
       <c r="B87" t="n">
-        <v>92.18158721923828</v>
+        <v>57.18619537353516</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>28.20763969421387</v>
+        <v>11</v>
       </c>
       <c r="B88" t="n">
-        <v>20.68033981323242</v>
+        <v>16.68823623657227</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>103.8000030517578</v>
+        <v>10.89999961853027</v>
       </c>
       <c r="B89" t="n">
-        <v>91.05312347412109</v>
+        <v>14.68805694580078</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>28.40352630615234</v>
+        <v>13.22233104705811</v>
       </c>
       <c r="B90" t="n">
-        <v>29.86652374267578</v>
+        <v>12.28285503387451</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>60.82272338867188</v>
+        <v>24.38785552978516</v>
       </c>
       <c r="B91" t="n">
-        <v>53.16263580322266</v>
+        <v>24.05537223815918</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>63.0476188659668</v>
+        <v>46.70000076293945</v>
       </c>
       <c r="B92" t="n">
-        <v>61.99195861816406</v>
+        <v>32.66379928588867</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>40</v>
+        <v>24.19047546386719</v>
       </c>
       <c r="B93" t="n">
-        <v>36.87960052490234</v>
+        <v>25.80780601501465</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>62.09523773193359</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="B94" t="n">
-        <v>53.76725769042969</v>
+        <v>21.99429130554199</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>40.47618865966797</v>
+        <v>15.118577003479</v>
       </c>
       <c r="B95" t="n">
-        <v>35.24392318725586</v>
+        <v>18.72936058044434</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>87.80000305175781</v>
+        <v>50.40000152587891</v>
       </c>
       <c r="B96" t="n">
-        <v>53.91171646118164</v>
+        <v>51.49254989624023</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>54.90000152587891</v>
+        <v>14.1304349899292</v>
       </c>
       <c r="B97" t="n">
-        <v>57.06547546386719</v>
+        <v>22.45876312255859</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>3.428011655807495</v>
+        <v>6.0724778175354</v>
       </c>
       <c r="B98" t="n">
-        <v>18.25922966003418</v>
+        <v>13.08581352233887</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>59.40000152587891</v>
+        <v>31.63565063476562</v>
       </c>
       <c r="B99" t="n">
-        <v>50.25788879394531</v>
+        <v>28.5356330871582</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2.938295841217041</v>
+        <v>11.56126499176025</v>
       </c>
       <c r="B100" t="n">
-        <v>17.79245376586914</v>
+        <v>15.62507629394531</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>58.70000076293945</v>
+        <v>20.47012710571289</v>
       </c>
       <c r="B101" t="n">
-        <v>46.67400741577148</v>
+        <v>19.53239059448242</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>85.69999694824219</v>
+        <v>62.09523773193359</v>
       </c>
       <c r="B102" t="n">
-        <v>84.79955291748047</v>
+        <v>60.09162902832031</v>
       </c>
     </row>
     <row r="103">
@@ -1253,95 +1253,95 @@
         <v>40</v>
       </c>
       <c r="B103" t="n">
-        <v>28.7396183013916</v>
+        <v>41.3222541809082</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>61.90476226806641</v>
+        <v>59.52381134033203</v>
       </c>
       <c r="B104" t="n">
-        <v>60.90769958496094</v>
+        <v>58.45169830322266</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>32.24206161499023</v>
+        <v>26.98412704467773</v>
       </c>
       <c r="B105" t="n">
-        <v>41.87126159667969</v>
+        <v>26.23761367797852</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>39.09999847412109</v>
+        <v>3.917727708816528</v>
       </c>
       <c r="B106" t="n">
-        <v>33.65589141845703</v>
+        <v>7.929886817932129</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>58</v>
+        <v>58.76591491699219</v>
       </c>
       <c r="B107" t="n">
-        <v>59.89590454101562</v>
+        <v>54.18055725097656</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>58</v>
+        <v>21.89999961853027</v>
       </c>
       <c r="B108" t="n">
-        <v>57.99983215332031</v>
+        <v>17.95315361022949</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>60.82272338867188</v>
+        <v>39.17727661132812</v>
       </c>
       <c r="B109" t="n">
-        <v>60.62348175048828</v>
+        <v>43.24948883056641</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>91.5</v>
+        <v>17.79999923706055</v>
       </c>
       <c r="B110" t="n">
-        <v>83.9136962890625</v>
+        <v>15.8432559967041</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>103.8000030517578</v>
+        <v>20</v>
       </c>
       <c r="B111" t="n">
-        <v>69.66098785400391</v>
+        <v>22.5797176361084</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>92.90000152587891</v>
+        <v>35.29999923706055</v>
       </c>
       <c r="B112" t="n">
-        <v>93.92959594726562</v>
+        <v>29.87068367004395</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>70.47618865966797</v>
+        <v>41</v>
       </c>
       <c r="B113" t="n">
-        <v>41.84063339233398</v>
+        <v>42.64296722412109</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>3.917727708816528</v>
+        <v>40.20000076293945</v>
       </c>
       <c r="B114" t="n">
-        <v>13.48669242858887</v>
+        <v>34.22240829467773</v>
       </c>
     </row>
   </sheetData>

--- a/labeled/Add_Eating/July/tcn_predictions_both_regression.xlsx
+++ b/labeled/Add_Eating/July/tcn_predictions_both_regression.xlsx
@@ -442,122 +442,122 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>60</v>
+        <v>9.162561416625977</v>
       </c>
       <c r="B2" t="n">
-        <v>61.0377197265625</v>
+        <v>8.515286445617676</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20.60000038146973</v>
+        <v>90.19999694824219</v>
       </c>
       <c r="B3" t="n">
-        <v>15.24424839019775</v>
+        <v>84.61133575439453</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>12.73261547088623</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="B4" t="n">
-        <v>11.17495536804199</v>
+        <v>17.25009155273438</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>37.59999847412109</v>
+        <v>24.5714282989502</v>
       </c>
       <c r="B5" t="n">
-        <v>30.63302993774414</v>
+        <v>17.24047470092773</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>34.37805938720703</v>
+        <v>40.59999847412109</v>
       </c>
       <c r="B6" t="n">
-        <v>35.17618179321289</v>
+        <v>30.85038757324219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>22.60000038146973</v>
+        <v>38.40000152587891</v>
       </c>
       <c r="B7" t="n">
-        <v>27.07966613769531</v>
+        <v>34.84799575805664</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>48</v>
+        <v>29.79999923706055</v>
       </c>
       <c r="B8" t="n">
-        <v>44.0576171875</v>
+        <v>16.82768058776855</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>28.7952995300293</v>
+        <v>39.09999847412109</v>
       </c>
       <c r="B9" t="n">
-        <v>27.69060707092285</v>
+        <v>45.84329223632812</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9.990205764770508</v>
+        <v>17.46031761169434</v>
       </c>
       <c r="B10" t="n">
-        <v>10.4569149017334</v>
+        <v>12.38865947723389</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20.33730125427246</v>
+        <v>26.44466209411621</v>
       </c>
       <c r="B11" t="n">
-        <v>24.45772933959961</v>
+        <v>17.38627815246582</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11.14285755157471</v>
+        <v>28</v>
       </c>
       <c r="B12" t="n">
-        <v>9.950004577636719</v>
+        <v>35.84884643554688</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>33.90000152587891</v>
+        <v>14.19999980926514</v>
       </c>
       <c r="B13" t="n">
-        <v>23.74174690246582</v>
+        <v>22.13624954223633</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>40</v>
+        <v>5.221674919128418</v>
       </c>
       <c r="B14" t="n">
-        <v>49.49699783325195</v>
+        <v>8.905632019042969</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>9.162561416625977</v>
+        <v>10.77075099945068</v>
       </c>
       <c r="B15" t="n">
-        <v>8.599762916564941</v>
+        <v>16.04064178466797</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>36.63075256347656</v>
+        <v>22.9187068939209</v>
       </c>
       <c r="B16" t="n">
-        <v>24.98045921325684</v>
+        <v>14.47385406494141</v>
       </c>
     </row>
     <row r="17">
@@ -565,783 +565,783 @@
         <v>39.68254089355469</v>
       </c>
       <c r="B17" t="n">
-        <v>40.43139266967773</v>
+        <v>36.46321868896484</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20.66601371765137</v>
+        <v>0.800000011920929</v>
       </c>
       <c r="B18" t="n">
-        <v>24.5894832611084</v>
+        <v>20.35693550109863</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>27.6785717010498</v>
+        <v>97.94319152832031</v>
       </c>
       <c r="B19" t="n">
-        <v>26.83601760864258</v>
+        <v>110.9547348022461</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>15.10000038146973</v>
+        <v>16.29999923706055</v>
       </c>
       <c r="B20" t="n">
-        <v>16.26782417297363</v>
+        <v>20.35868072509766</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>80</v>
+        <v>19.64285659790039</v>
       </c>
       <c r="B21" t="n">
-        <v>74.27167510986328</v>
+        <v>16.50208473205566</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>13.4285717010498</v>
+        <v>20.60000038146973</v>
       </c>
       <c r="B22" t="n">
-        <v>17.29689407348633</v>
+        <v>14.02850437164307</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>11.11111068725586</v>
+        <v>57.20000076293945</v>
       </c>
       <c r="B23" t="n">
-        <v>11.31690406799316</v>
+        <v>33.95404434204102</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6.660137176513672</v>
+        <v>22.89999961853027</v>
       </c>
       <c r="B24" t="n">
-        <v>16.43674659729004</v>
+        <v>22.99517250061035</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>27.90476226806641</v>
+        <v>8.952381134033203</v>
       </c>
       <c r="B25" t="n">
-        <v>33.58940124511719</v>
+        <v>30.51654624938965</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>16.5714282989502</v>
+        <v>99.20635223388672</v>
       </c>
       <c r="B26" t="n">
-        <v>17.44294738769531</v>
+        <v>79.02333831787109</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>17.80952453613281</v>
+        <v>39.5</v>
       </c>
       <c r="B27" t="n">
-        <v>11.96884632110596</v>
+        <v>58.97380828857422</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>15.083251953125</v>
+        <v>18.75</v>
       </c>
       <c r="B28" t="n">
-        <v>14.37854671478271</v>
+        <v>59.10289001464844</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>32.41919708251953</v>
+        <v>19.84127044677734</v>
       </c>
       <c r="B29" t="n">
-        <v>38.05093002319336</v>
+        <v>17.66682434082031</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>15.08875751495361</v>
+        <v>9.142857551574707</v>
       </c>
       <c r="B30" t="n">
-        <v>15.70514869689941</v>
+        <v>17.11967849731445</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>39.68254089355469</v>
+        <v>10.7737512588501</v>
       </c>
       <c r="B31" t="n">
-        <v>46.64896011352539</v>
+        <v>10.19860553741455</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>25.46523094177246</v>
+        <v>44.70000076293945</v>
       </c>
       <c r="B32" t="n">
-        <v>24.01793670654297</v>
+        <v>32.17421340942383</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>91.5</v>
+        <v>3.917727708816528</v>
       </c>
       <c r="B33" t="n">
-        <v>95.29362487792969</v>
+        <v>10.07769012451172</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>80</v>
+        <v>13.71204662322998</v>
       </c>
       <c r="B34" t="n">
-        <v>72.04434204101562</v>
+        <v>22.84538841247559</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>35.16160583496094</v>
+        <v>12.69841289520264</v>
       </c>
       <c r="B35" t="n">
-        <v>28.14466285705566</v>
+        <v>31.60939979553223</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>10.4761905670166</v>
+        <v>22.51984214782715</v>
       </c>
       <c r="B36" t="n">
-        <v>13.55770301818848</v>
+        <v>33.65222930908203</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>35.20000076293945</v>
+        <v>19.84127044677734</v>
       </c>
       <c r="B37" t="n">
-        <v>33.27633666992188</v>
+        <v>21.35406303405762</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>51.90989303588867</v>
+        <v>13.22233104705811</v>
       </c>
       <c r="B38" t="n">
-        <v>47.93557739257812</v>
+        <v>14.48591232299805</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>43.79999923706055</v>
+        <v>22.60000038146973</v>
       </c>
       <c r="B39" t="n">
-        <v>45.83195877075195</v>
+        <v>29.12475204467773</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>23.5238094329834</v>
+        <v>60</v>
       </c>
       <c r="B40" t="n">
-        <v>24.1537914276123</v>
+        <v>77.43804931640625</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>39.68254089355469</v>
+        <v>24.68168449401855</v>
       </c>
       <c r="B41" t="n">
-        <v>44.95416259765625</v>
+        <v>14.93087482452393</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>11.65524005889893</v>
+        <v>15.90476226806641</v>
       </c>
       <c r="B42" t="n">
-        <v>14.82961654663086</v>
+        <v>10.46953678131104</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>14.66666698455811</v>
+        <v>20</v>
       </c>
       <c r="B43" t="n">
-        <v>18.7154541015625</v>
+        <v>34.90014266967773</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>60</v>
+        <v>11.50793647766113</v>
       </c>
       <c r="B44" t="n">
-        <v>57.28807830810547</v>
+        <v>16.5994873046875</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>23.01665115356445</v>
+        <v>27.32615089416504</v>
       </c>
       <c r="B45" t="n">
-        <v>26.64728736877441</v>
+        <v>21.53721809387207</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>19.0476188659668</v>
+        <v>31.80952453613281</v>
       </c>
       <c r="B46" t="n">
-        <v>26.51895332336426</v>
+        <v>30.93127822875977</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>20</v>
+        <v>37.79999923706055</v>
       </c>
       <c r="B47" t="n">
-        <v>34.94650650024414</v>
+        <v>23.32937622070312</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>61.40000152587891</v>
+        <v>16.5714282989502</v>
       </c>
       <c r="B48" t="n">
-        <v>64.18421173095703</v>
+        <v>19.73823928833008</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>41.52381134033203</v>
+        <v>59.40000152587891</v>
       </c>
       <c r="B49" t="n">
-        <v>37.40254974365234</v>
+        <v>64.84433746337891</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>32.24206161499023</v>
+        <v>9.027777671813965</v>
       </c>
       <c r="B50" t="n">
-        <v>33.51081848144531</v>
+        <v>15.8610897064209</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="B51" t="n">
-        <v>26.57788848876953</v>
+        <v>87.48452758789062</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>90.19999694824219</v>
+        <v>7.783251285552979</v>
       </c>
       <c r="B52" t="n">
-        <v>83.15576171875</v>
+        <v>10.69479751586914</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>23.60000038146973</v>
+        <v>23.21428489685059</v>
       </c>
       <c r="B53" t="n">
-        <v>23.96372032165527</v>
+        <v>13.72163772583008</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>21.05778694152832</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="B54" t="n">
-        <v>19.93966293334961</v>
+        <v>19.9989185333252</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>6.547618865966797</v>
+        <v>70.80000305175781</v>
       </c>
       <c r="B55" t="n">
-        <v>8.342134475708008</v>
+        <v>90.56932830810547</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>21.39999961853027</v>
+        <v>30.15872955322266</v>
       </c>
       <c r="B56" t="n">
-        <v>20.8316822052002</v>
+        <v>22.94293785095215</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>21.89999961853027</v>
+        <v>40</v>
       </c>
       <c r="B57" t="n">
-        <v>21.28005409240723</v>
+        <v>62.44239044189453</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>9.06403923034668</v>
+        <v>19.0476188659668</v>
       </c>
       <c r="B58" t="n">
-        <v>18.51709747314453</v>
+        <v>25.87075233459473</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>71.80000305175781</v>
+        <v>59.52381134033203</v>
       </c>
       <c r="B59" t="n">
-        <v>75.739990234375</v>
+        <v>37.57720947265625</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>18</v>
+        <v>13.5238094329834</v>
       </c>
       <c r="B60" t="n">
-        <v>21.06497001647949</v>
+        <v>13.64643955230713</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>17.10000038146973</v>
+        <v>24.70000076293945</v>
       </c>
       <c r="B61" t="n">
-        <v>23.30783843994141</v>
+        <v>18.94382476806641</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>22.13516235351562</v>
+        <v>25.5</v>
       </c>
       <c r="B62" t="n">
-        <v>20.47330093383789</v>
+        <v>26.2447681427002</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>16.96428489685059</v>
+        <v>40.45053863525391</v>
       </c>
       <c r="B63" t="n">
-        <v>12.5278148651123</v>
+        <v>22.73573303222656</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>20</v>
+        <v>25.79999923706055</v>
       </c>
       <c r="B64" t="n">
-        <v>20.0888671875</v>
+        <v>26.64831733703613</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>39.68254089355469</v>
+        <v>15.083251953125</v>
       </c>
       <c r="B65" t="n">
-        <v>44.47504425048828</v>
+        <v>7.924952030181885</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>23.11459350585938</v>
+        <v>32.24206161499023</v>
       </c>
       <c r="B66" t="n">
-        <v>23.68696022033691</v>
+        <v>22.91329193115234</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>20</v>
+        <v>22.09523773193359</v>
       </c>
       <c r="B67" t="n">
-        <v>31.2418384552002</v>
+        <v>39.6708869934082</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>44.79999923706055</v>
+        <v>18.19047546386719</v>
       </c>
       <c r="B68" t="n">
-        <v>45.25007629394531</v>
+        <v>18.8795337677002</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>14.6245059967041</v>
+        <v>13.2380952835083</v>
       </c>
       <c r="B69" t="n">
-        <v>15.35816383361816</v>
+        <v>17.01884269714355</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>80</v>
+        <v>22.5</v>
       </c>
       <c r="B70" t="n">
-        <v>71.99905395507812</v>
+        <v>16.79475402832031</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>20</v>
+        <v>29.60000038146973</v>
       </c>
       <c r="B71" t="n">
-        <v>31.21963691711426</v>
+        <v>21.09838104248047</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>35.90000152587891</v>
+        <v>18.65079307556152</v>
       </c>
       <c r="B72" t="n">
-        <v>38.19002532958984</v>
+        <v>13.58133125305176</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>29.60000038146973</v>
+        <v>68.28571319580078</v>
       </c>
       <c r="B73" t="n">
-        <v>25.05302619934082</v>
+        <v>82.56175994873047</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>19.84127044677734</v>
+        <v>26.98412704467773</v>
       </c>
       <c r="B74" t="n">
-        <v>27.3168888092041</v>
+        <v>22.79294013977051</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>8.275861740112305</v>
+        <v>18.70000076293945</v>
       </c>
       <c r="B75" t="n">
-        <v>20.05484008789062</v>
+        <v>17.27608871459961</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>6.206896781921387</v>
+        <v>13.89999961853027</v>
       </c>
       <c r="B76" t="n">
-        <v>11.4210901260376</v>
+        <v>17.84830474853516</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>13.88888931274414</v>
+        <v>11.7142858505249</v>
       </c>
       <c r="B77" t="n">
-        <v>17.77402114868164</v>
+        <v>14.41477489471436</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>60</v>
+        <v>12.53672885894775</v>
       </c>
       <c r="B78" t="n">
-        <v>63.71698379516602</v>
+        <v>15.26077079772949</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>58.70000076293945</v>
+        <v>7.737512111663818</v>
       </c>
       <c r="B79" t="n">
-        <v>54.8780403137207</v>
+        <v>12.78902626037598</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>39.5</v>
+        <v>9.809523582458496</v>
       </c>
       <c r="B80" t="n">
-        <v>44.15721893310547</v>
+        <v>11.3807258605957</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>17.36111068725586</v>
+        <v>60</v>
       </c>
       <c r="B81" t="n">
-        <v>20.97534942626953</v>
+        <v>78.17948913574219</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>57</v>
+        <v>99.20635223388672</v>
       </c>
       <c r="B82" t="n">
-        <v>52.78530120849609</v>
+        <v>101.6842956542969</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>73.40000152587891</v>
+        <v>18.55158805847168</v>
       </c>
       <c r="B83" t="n">
-        <v>81.25955200195312</v>
+        <v>20.69888687133789</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>21</v>
+        <v>103.8000030517578</v>
       </c>
       <c r="B84" t="n">
-        <v>16.44359016418457</v>
+        <v>94.96818542480469</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>23.5</v>
+        <v>97.94319152832031</v>
       </c>
       <c r="B85" t="n">
-        <v>25.71222496032715</v>
+        <v>76.27256011962891</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>25.6611156463623</v>
+        <v>20.20000076293945</v>
       </c>
       <c r="B86" t="n">
-        <v>24.41497993469238</v>
+        <v>23.58082389831543</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>60</v>
+        <v>69.63761138916016</v>
       </c>
       <c r="B87" t="n">
-        <v>57.18619537353516</v>
+        <v>71.81753540039062</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>11</v>
+        <v>26.28968238830566</v>
       </c>
       <c r="B88" t="n">
-        <v>16.68823623657227</v>
+        <v>31.91581916809082</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>10.89999961853027</v>
+        <v>7.900000095367432</v>
       </c>
       <c r="B89" t="n">
-        <v>14.68805694580078</v>
+        <v>30.16147232055664</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>13.22233104705811</v>
+        <v>51.90989303588867</v>
       </c>
       <c r="B90" t="n">
-        <v>12.28285503387451</v>
+        <v>51.19277954101562</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>24.38785552978516</v>
+        <v>71.80000305175781</v>
       </c>
       <c r="B91" t="n">
-        <v>24.05537223815918</v>
+        <v>26.85123825073242</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>46.70000076293945</v>
+        <v>58.70000076293945</v>
       </c>
       <c r="B92" t="n">
-        <v>32.66379928588867</v>
+        <v>44.35563278198242</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>24.19047546386719</v>
+        <v>24.68168449401855</v>
       </c>
       <c r="B93" t="n">
-        <v>25.80780601501465</v>
+        <v>28.32527160644531</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>22.29999923706055</v>
+        <v>17.29999923706055</v>
       </c>
       <c r="B94" t="n">
-        <v>21.99429130554199</v>
+        <v>16.5869083404541</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>15.118577003479</v>
+        <v>129.3000030517578</v>
       </c>
       <c r="B95" t="n">
-        <v>18.72936058044434</v>
+        <v>50.99778747558594</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>50.40000152587891</v>
+        <v>19.84127044677734</v>
       </c>
       <c r="B96" t="n">
-        <v>51.49254989624023</v>
+        <v>42.29328918457031</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>14.1304349899292</v>
+        <v>99.20635223388672</v>
       </c>
       <c r="B97" t="n">
-        <v>22.45876312255859</v>
+        <v>100.0838623046875</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>6.0724778175354</v>
+        <v>54.90000152587891</v>
       </c>
       <c r="B98" t="n">
-        <v>13.08581352233887</v>
+        <v>91.59323120117188</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>31.63565063476562</v>
+        <v>15.0476188659668</v>
       </c>
       <c r="B99" t="n">
-        <v>28.5356330871582</v>
+        <v>17.21417427062988</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>11.56126499176025</v>
+        <v>40.25465393066406</v>
       </c>
       <c r="B100" t="n">
-        <v>15.62507629394531</v>
+        <v>31.69048118591309</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>20.47012710571289</v>
+        <v>18.70000076293945</v>
       </c>
       <c r="B101" t="n">
-        <v>19.53239059448242</v>
+        <v>14.48023509979248</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>62.09523773193359</v>
+        <v>11.56126499176025</v>
       </c>
       <c r="B102" t="n">
-        <v>60.09162902832031</v>
+        <v>26.01250267028809</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>40</v>
+        <v>20.27424049377441</v>
       </c>
       <c r="B103" t="n">
-        <v>41.3222541809082</v>
+        <v>23.25353813171387</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>59.52381134033203</v>
+        <v>28.10000038146973</v>
       </c>
       <c r="B104" t="n">
-        <v>58.45169830322266</v>
+        <v>27.06918716430664</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>26.98412704467773</v>
+        <v>29.10000038146973</v>
       </c>
       <c r="B105" t="n">
-        <v>26.23761367797852</v>
+        <v>25.61327171325684</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>3.917727708816528</v>
+        <v>22.09523773193359</v>
       </c>
       <c r="B106" t="n">
-        <v>7.929886817932129</v>
+        <v>25.00237655639648</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>58.76591491699219</v>
+        <v>38.19047546386719</v>
       </c>
       <c r="B107" t="n">
-        <v>54.18055725097656</v>
+        <v>26.88409423828125</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>21.89999961853027</v>
+        <v>12.54940700531006</v>
       </c>
       <c r="B108" t="n">
-        <v>17.95315361022949</v>
+        <v>13.82671165466309</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>39.17727661132812</v>
+        <v>79.36508178710938</v>
       </c>
       <c r="B109" t="n">
-        <v>43.24948883056641</v>
+        <v>67.95281982421875</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>17.79999923706055</v>
+        <v>31</v>
       </c>
       <c r="B110" t="n">
-        <v>15.8432559967041</v>
+        <v>24.26359939575195</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>20</v>
+        <v>12.30158710479736</v>
       </c>
       <c r="B111" t="n">
-        <v>22.5797176361084</v>
+        <v>8.778467178344727</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>35.29999923706055</v>
+        <v>19.58863830566406</v>
       </c>
       <c r="B112" t="n">
-        <v>29.87068367004395</v>
+        <v>28.24709510803223</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>41</v>
+        <v>19.5</v>
       </c>
       <c r="B113" t="n">
-        <v>42.64296722412109</v>
+        <v>13.28280353546143</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>40.20000076293945</v>
+        <v>17.23800277709961</v>
       </c>
       <c r="B114" t="n">
-        <v>34.22240829467773</v>
+        <v>17.08632278442383</v>
       </c>
     </row>
   </sheetData>

--- a/labeled/Add_Eating/July/tcn_predictions_both_regression.xlsx
+++ b/labeled/Add_Eating/July/tcn_predictions_both_regression.xlsx
@@ -442,906 +442,906 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>9.162561416625977</v>
+        <v>38.39373016357422</v>
       </c>
       <c r="B2" t="n">
-        <v>8.515286445617676</v>
+        <v>24.52867889404297</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90.19999694824219</v>
+        <v>21.89999961853027</v>
       </c>
       <c r="B3" t="n">
-        <v>84.61133575439453</v>
+        <v>22.74802589416504</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>22.20000076293945</v>
+        <v>100</v>
       </c>
       <c r="B4" t="n">
-        <v>17.25009155273438</v>
+        <v>93.95877075195312</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>24.5714282989502</v>
+        <v>13.32027435302734</v>
       </c>
       <c r="B5" t="n">
-        <v>17.24047470092773</v>
+        <v>13.59421920776367</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>40.59999847412109</v>
+        <v>39.17727661132812</v>
       </c>
       <c r="B6" t="n">
-        <v>30.85038757324219</v>
+        <v>40.20397186279297</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>38.40000152587891</v>
+        <v>25.6611156463623</v>
       </c>
       <c r="B7" t="n">
-        <v>34.84799575805664</v>
+        <v>22.13090896606445</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>29.79999923706055</v>
+        <v>28</v>
       </c>
       <c r="B8" t="n">
-        <v>16.82768058776855</v>
+        <v>19.05547332763672</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>39.09999847412109</v>
+        <v>13.89999961853027</v>
       </c>
       <c r="B9" t="n">
-        <v>45.84329223632812</v>
+        <v>21.39022636413574</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>17.46031761169434</v>
+        <v>87.80000305175781</v>
       </c>
       <c r="B10" t="n">
-        <v>12.38865947723389</v>
+        <v>87.52914428710938</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>26.44466209411621</v>
+        <v>14.6245059967041</v>
       </c>
       <c r="B11" t="n">
-        <v>17.38627815246582</v>
+        <v>11.53185844421387</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>28</v>
+        <v>10.4761905670166</v>
       </c>
       <c r="B12" t="n">
-        <v>35.84884643554688</v>
+        <v>21.53850746154785</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>14.19999980926514</v>
+        <v>37.59999847412109</v>
       </c>
       <c r="B13" t="n">
-        <v>22.13624954223633</v>
+        <v>14.08118152618408</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5.221674919128418</v>
+        <v>59.52381134033203</v>
       </c>
       <c r="B14" t="n">
-        <v>8.905632019042969</v>
+        <v>51.77595138549805</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10.77075099945068</v>
+        <v>26.05288887023926</v>
       </c>
       <c r="B15" t="n">
-        <v>16.04064178466797</v>
+        <v>38.62724685668945</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>22.9187068939209</v>
+        <v>13.5238094329834</v>
       </c>
       <c r="B16" t="n">
-        <v>14.47385406494141</v>
+        <v>10.62777900695801</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>39.68254089355469</v>
+        <v>62.09523773193359</v>
       </c>
       <c r="B17" t="n">
-        <v>36.46321868896484</v>
+        <v>54.75491333007812</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.800000011920929</v>
+        <v>73.5</v>
       </c>
       <c r="B18" t="n">
-        <v>20.35693550109863</v>
+        <v>49.79043960571289</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97.94319152832031</v>
+        <v>39.68254089355469</v>
       </c>
       <c r="B19" t="n">
-        <v>110.9547348022461</v>
+        <v>39.99549102783203</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>16.29999923706055</v>
+        <v>20</v>
       </c>
       <c r="B20" t="n">
-        <v>20.35868072509766</v>
+        <v>41.87807464599609</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>19.64285659790039</v>
+        <v>39.17727661132812</v>
       </c>
       <c r="B21" t="n">
-        <v>16.50208473205566</v>
+        <v>42.53378295898438</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20.60000038146973</v>
+        <v>63.17335891723633</v>
       </c>
       <c r="B22" t="n">
-        <v>14.02850437164307</v>
+        <v>40.66704559326172</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>57.20000076293945</v>
+        <v>14.20176315307617</v>
       </c>
       <c r="B23" t="n">
-        <v>33.95404434204102</v>
+        <v>13.4672155380249</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22.89999961853027</v>
+        <v>2.938295841217041</v>
       </c>
       <c r="B24" t="n">
-        <v>22.99517250061035</v>
+        <v>6.832663536071777</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>8.952381134033203</v>
+        <v>12.32741641998291</v>
       </c>
       <c r="B25" t="n">
-        <v>30.51654624938965</v>
+        <v>10.40159034729004</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>99.20635223388672</v>
+        <v>42.19047546386719</v>
       </c>
       <c r="B26" t="n">
-        <v>79.02333831787109</v>
+        <v>21.06487464904785</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>39.5</v>
+        <v>24.00793647766113</v>
       </c>
       <c r="B27" t="n">
-        <v>58.97380828857422</v>
+        <v>14.07598972320557</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>18.75</v>
+        <v>23.5238094329834</v>
       </c>
       <c r="B28" t="n">
-        <v>59.10289001464844</v>
+        <v>30.78339195251465</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>19.84127044677734</v>
+        <v>11.70634937286377</v>
       </c>
       <c r="B29" t="n">
-        <v>17.66682434082031</v>
+        <v>11.59224891662598</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>9.142857551574707</v>
+        <v>17.39999961853027</v>
       </c>
       <c r="B30" t="n">
-        <v>17.11967849731445</v>
+        <v>13.75630950927734</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>10.7737512588501</v>
+        <v>33.70000076293945</v>
       </c>
       <c r="B31" t="n">
-        <v>10.19860553741455</v>
+        <v>19.88212776184082</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>44.70000076293945</v>
+        <v>18.19047546386719</v>
       </c>
       <c r="B32" t="n">
-        <v>32.17421340942383</v>
+        <v>15.15256595611572</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3.917727708816528</v>
+        <v>19.5</v>
       </c>
       <c r="B33" t="n">
-        <v>10.07769012451172</v>
+        <v>11.72210121154785</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>13.71204662322998</v>
+        <v>22.70000076293945</v>
       </c>
       <c r="B34" t="n">
-        <v>22.84538841247559</v>
+        <v>21.70554542541504</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>12.69841289520264</v>
+        <v>9.683794021606445</v>
       </c>
       <c r="B35" t="n">
-        <v>31.60939979553223</v>
+        <v>11.59239673614502</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>22.51984214782715</v>
+        <v>58.76591491699219</v>
       </c>
       <c r="B36" t="n">
-        <v>33.65222930908203</v>
+        <v>65.42913055419922</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>19.84127044677734</v>
+        <v>21.13095283508301</v>
       </c>
       <c r="B37" t="n">
-        <v>21.35406303405762</v>
+        <v>13.02682971954346</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>13.22233104705811</v>
+        <v>19.58863830566406</v>
       </c>
       <c r="B38" t="n">
-        <v>14.48591232299805</v>
+        <v>28.97674179077148</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>22.60000038146973</v>
+        <v>54.90000152587891</v>
       </c>
       <c r="B39" t="n">
-        <v>29.12475204467773</v>
+        <v>62.71205520629883</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>60</v>
+        <v>26.05288887023926</v>
       </c>
       <c r="B40" t="n">
-        <v>77.43804931640625</v>
+        <v>27.42791938781738</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>24.68168449401855</v>
+        <v>17.26190567016602</v>
       </c>
       <c r="B41" t="n">
-        <v>14.93087482452393</v>
+        <v>18.28800392150879</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>15.90476226806641</v>
+        <v>14.39764976501465</v>
       </c>
       <c r="B42" t="n">
-        <v>10.46953678131104</v>
+        <v>14.39058589935303</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="B43" t="n">
-        <v>34.90014266967773</v>
+        <v>49.76860809326172</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>11.50793647766113</v>
+        <v>8.380952835083008</v>
       </c>
       <c r="B44" t="n">
-        <v>16.5994873046875</v>
+        <v>37.20895385742188</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>27.32615089416504</v>
+        <v>22.13516235351562</v>
       </c>
       <c r="B45" t="n">
-        <v>21.53721809387207</v>
+        <v>18.58597564697266</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>31.80952453613281</v>
+        <v>14.58333301544189</v>
       </c>
       <c r="B46" t="n">
-        <v>30.93127822875977</v>
+        <v>10.82790756225586</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>37.79999923706055</v>
+        <v>32.41919708251953</v>
       </c>
       <c r="B47" t="n">
-        <v>23.32937622070312</v>
+        <v>26.48183250427246</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>16.5714282989502</v>
+        <v>20.53571510314941</v>
       </c>
       <c r="B48" t="n">
-        <v>19.73823928833008</v>
+        <v>18.85612106323242</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>59.40000152587891</v>
+        <v>16.56746101379395</v>
       </c>
       <c r="B49" t="n">
-        <v>64.84433746337891</v>
+        <v>11.6419849395752</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>9.027777671813965</v>
+        <v>11.43984222412109</v>
       </c>
       <c r="B50" t="n">
-        <v>15.8610897064209</v>
+        <v>10.74986934661865</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>80</v>
+        <v>19.19686508178711</v>
       </c>
       <c r="B51" t="n">
-        <v>87.48452758789062</v>
+        <v>25.86443138122559</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>7.783251285552979</v>
+        <v>23.21428489685059</v>
       </c>
       <c r="B52" t="n">
-        <v>10.69479751586914</v>
+        <v>16.28202819824219</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>23.21428489685059</v>
+        <v>40.45053863525391</v>
       </c>
       <c r="B53" t="n">
-        <v>13.72163772583008</v>
+        <v>29.42146492004395</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>21.39999961853027</v>
+        <v>11.33333301544189</v>
       </c>
       <c r="B54" t="n">
-        <v>19.9989185333252</v>
+        <v>8.839282035827637</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>70.80000305175781</v>
+        <v>38.09523773193359</v>
       </c>
       <c r="B55" t="n">
-        <v>90.56932830810547</v>
+        <v>45.23451995849609</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>30.15872955322266</v>
+        <v>17.70000076293945</v>
       </c>
       <c r="B56" t="n">
-        <v>22.94293785095215</v>
+        <v>23.20526695251465</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>40</v>
+        <v>19.84127044677734</v>
       </c>
       <c r="B57" t="n">
-        <v>62.44239044189453</v>
+        <v>16.39069366455078</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>19.0476188659668</v>
+        <v>160.1999969482422</v>
       </c>
       <c r="B58" t="n">
-        <v>25.87075233459473</v>
+        <v>161.3703002929688</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>59.52381134033203</v>
+        <v>25.20000076293945</v>
       </c>
       <c r="B59" t="n">
-        <v>37.57720947265625</v>
+        <v>39.2181510925293</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>13.5238094329834</v>
+        <v>35.20000076293945</v>
       </c>
       <c r="B60" t="n">
-        <v>13.64643955230713</v>
+        <v>23.99433708190918</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>24.70000076293945</v>
+        <v>8.630952835083008</v>
       </c>
       <c r="B61" t="n">
-        <v>18.94382476806641</v>
+        <v>11.06290245056152</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>25.5</v>
+        <v>38.40000152587891</v>
       </c>
       <c r="B62" t="n">
-        <v>26.2447681427002</v>
+        <v>36.92121505737305</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>40.45053863525391</v>
+        <v>39.68254089355469</v>
       </c>
       <c r="B63" t="n">
-        <v>22.73573303222656</v>
+        <v>41.0105094909668</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>25.79999923706055</v>
+        <v>11.7142858505249</v>
       </c>
       <c r="B64" t="n">
-        <v>26.64831733703613</v>
+        <v>20.45207023620605</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>15.083251953125</v>
+        <v>45.52381134033203</v>
       </c>
       <c r="B65" t="n">
-        <v>7.924952030181885</v>
+        <v>25.59259414672852</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>32.24206161499023</v>
+        <v>21.39999961853027</v>
       </c>
       <c r="B66" t="n">
-        <v>22.91329193115234</v>
+        <v>18.38569831848145</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>22.09523773193359</v>
+        <v>42.09999847412109</v>
       </c>
       <c r="B67" t="n">
-        <v>39.6708869934082</v>
+        <v>43.12036895751953</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>18.19047546386719</v>
+        <v>10.4761905670166</v>
       </c>
       <c r="B68" t="n">
-        <v>18.8795337677002</v>
+        <v>15.53624153137207</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>13.2380952835083</v>
+        <v>12.73261547088623</v>
       </c>
       <c r="B69" t="n">
-        <v>17.01884269714355</v>
+        <v>15.20753955841064</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>22.5</v>
+        <v>19.79999923706055</v>
       </c>
       <c r="B70" t="n">
-        <v>16.79475402832031</v>
+        <v>31.09541702270508</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>29.60000038146973</v>
+        <v>59.52381134033203</v>
       </c>
       <c r="B71" t="n">
-        <v>21.09838104248047</v>
+        <v>61.11734390258789</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>18.65079307556152</v>
+        <v>11.60000038146973</v>
       </c>
       <c r="B72" t="n">
-        <v>13.58133125305176</v>
+        <v>11.69350147247314</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>68.28571319580078</v>
+        <v>27.32615089416504</v>
       </c>
       <c r="B73" t="n">
-        <v>82.56175994873047</v>
+        <v>21.72577857971191</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>26.98412704467773</v>
+        <v>54.66666793823242</v>
       </c>
       <c r="B74" t="n">
-        <v>22.79294013977051</v>
+        <v>61.48516082763672</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>18.70000076293945</v>
+        <v>27.18253898620605</v>
       </c>
       <c r="B75" t="n">
-        <v>17.27608871459961</v>
+        <v>13.52665233612061</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>13.89999961853027</v>
+        <v>8.227228164672852</v>
       </c>
       <c r="B76" t="n">
-        <v>17.84830474853516</v>
+        <v>10.0368185043335</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>11.7142858505249</v>
+        <v>13.2380952835083</v>
       </c>
       <c r="B77" t="n">
-        <v>14.41477489471436</v>
+        <v>18.89632606506348</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>12.53672885894775</v>
+        <v>38.09999847412109</v>
       </c>
       <c r="B78" t="n">
-        <v>15.26077079772949</v>
+        <v>21.95417594909668</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>7.737512111663818</v>
+        <v>15.118577003479</v>
       </c>
       <c r="B79" t="n">
-        <v>12.78902626037598</v>
+        <v>21.4273681640625</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>9.809523582458496</v>
+        <v>11.11111068725586</v>
       </c>
       <c r="B80" t="n">
-        <v>11.3807258605957</v>
+        <v>15.28528785705566</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>60</v>
+        <v>28.7952995300293</v>
       </c>
       <c r="B81" t="n">
-        <v>78.17948913574219</v>
+        <v>36.41077423095703</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>99.20635223388672</v>
+        <v>10.34482765197754</v>
       </c>
       <c r="B82" t="n">
-        <v>101.6842956542969</v>
+        <v>14.87569618225098</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>18.55158805847168</v>
+        <v>69.90476226806641</v>
       </c>
       <c r="B83" t="n">
-        <v>20.69888687133789</v>
+        <v>70.50358581542969</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>103.8000030517578</v>
+        <v>26.10000038146973</v>
       </c>
       <c r="B84" t="n">
-        <v>94.96818542480469</v>
+        <v>20.60855674743652</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>97.94319152832031</v>
+        <v>5.320197105407715</v>
       </c>
       <c r="B85" t="n">
-        <v>76.27256011962891</v>
+        <v>17.17323303222656</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>20.20000076293945</v>
+        <v>80</v>
       </c>
       <c r="B86" t="n">
-        <v>23.58082389831543</v>
+        <v>77.82028198242188</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>69.63761138916016</v>
+        <v>59.52381134033203</v>
       </c>
       <c r="B87" t="n">
-        <v>71.81753540039062</v>
+        <v>46.8597412109375</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>26.28968238830566</v>
+        <v>60</v>
       </c>
       <c r="B88" t="n">
-        <v>31.91581916809082</v>
+        <v>67.04998779296875</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>7.900000095367432</v>
+        <v>92.90000152587891</v>
       </c>
       <c r="B89" t="n">
-        <v>30.16147232055664</v>
+        <v>50.84789657592773</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>51.90989303588867</v>
+        <v>99.20635223388672</v>
       </c>
       <c r="B90" t="n">
-        <v>51.19277954101562</v>
+        <v>93.33135223388672</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>71.80000305175781</v>
+        <v>9.990205764770508</v>
       </c>
       <c r="B91" t="n">
-        <v>26.85123825073242</v>
+        <v>12.44265365600586</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>58.70000076293945</v>
+        <v>36</v>
       </c>
       <c r="B92" t="n">
-        <v>44.35563278198242</v>
+        <v>23.1699047088623</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>24.68168449401855</v>
+        <v>29.10000038146973</v>
       </c>
       <c r="B93" t="n">
-        <v>28.32527160644531</v>
+        <v>18.46470260620117</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>17.29999923706055</v>
+        <v>21.5475025177002</v>
       </c>
       <c r="B94" t="n">
-        <v>16.5869083404541</v>
+        <v>21.73917961120605</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129.3000030517578</v>
+        <v>27.90476226806641</v>
       </c>
       <c r="B95" t="n">
-        <v>50.99778747558594</v>
+        <v>21.29885101318359</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>19.84127044677734</v>
+        <v>79.36508178710938</v>
       </c>
       <c r="B96" t="n">
-        <v>42.29328918457031</v>
+        <v>77.59984588623047</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>99.20635223388672</v>
+        <v>10.24630546569824</v>
       </c>
       <c r="B97" t="n">
-        <v>100.0838623046875</v>
+        <v>14.16143894195557</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>54.90000152587891</v>
+        <v>25.5</v>
       </c>
       <c r="B98" t="n">
-        <v>91.59323120117188</v>
+        <v>32.91664886474609</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>15.0476188659668</v>
+        <v>22.9187068939209</v>
       </c>
       <c r="B99" t="n">
-        <v>17.21417427062988</v>
+        <v>23.10127639770508</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>40.25465393066406</v>
+        <v>13.22233104705811</v>
       </c>
       <c r="B100" t="n">
-        <v>31.69048118591309</v>
+        <v>18.7010440826416</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>18.70000076293945</v>
+        <v>79.36508178710938</v>
       </c>
       <c r="B101" t="n">
-        <v>14.48023509979248</v>
+        <v>75.16810607910156</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>11.56126499176025</v>
+        <v>100</v>
       </c>
       <c r="B102" t="n">
-        <v>26.01250267028809</v>
+        <v>92.87579345703125</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>20.27424049377441</v>
+        <v>45</v>
       </c>
       <c r="B103" t="n">
-        <v>23.25353813171387</v>
+        <v>39.34627914428711</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>28.10000038146973</v>
+        <v>35.5</v>
       </c>
       <c r="B104" t="n">
-        <v>27.06918716430664</v>
+        <v>17.35833549499512</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>29.10000038146973</v>
+        <v>44.46620941162109</v>
       </c>
       <c r="B105" t="n">
-        <v>25.61327171325684</v>
+        <v>17.67758560180664</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>22.09523773193359</v>
+        <v>25.79365158081055</v>
       </c>
       <c r="B106" t="n">
-        <v>25.00237655639648</v>
+        <v>15.09021472930908</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>38.19047546386719</v>
+        <v>12.54940700531006</v>
       </c>
       <c r="B107" t="n">
-        <v>26.88409423828125</v>
+        <v>14.04097652435303</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>12.54940700531006</v>
+        <v>19.84127044677734</v>
       </c>
       <c r="B108" t="n">
-        <v>13.82671165466309</v>
+        <v>36.64452743530273</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>79.36508178710938</v>
+        <v>18.70000076293945</v>
       </c>
       <c r="B109" t="n">
-        <v>67.95281982421875</v>
+        <v>39.85103607177734</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="B110" t="n">
-        <v>24.26359939575195</v>
+        <v>52.34365081787109</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>12.30158710479736</v>
+        <v>25.39682579040527</v>
       </c>
       <c r="B111" t="n">
-        <v>8.778467178344727</v>
+        <v>10.03079891204834</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>19.58863830566406</v>
+        <v>11.2380952835083</v>
       </c>
       <c r="B112" t="n">
-        <v>28.24709510803223</v>
+        <v>36.36631393432617</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>19.5</v>
+        <v>28.20763969421387</v>
       </c>
       <c r="B113" t="n">
-        <v>13.28280353546143</v>
+        <v>22.73378372192383</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>17.23800277709961</v>
+        <v>85.69999694824219</v>
       </c>
       <c r="B114" t="n">
-        <v>17.08632278442383</v>
+        <v>65.66698455810547</v>
       </c>
     </row>
   </sheetData>
